--- a/data/GreatLink/GreatLink Income Bond_Dividends.xlsx
+++ b/data/GreatLink/GreatLink Income Bond_Dividends.xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="DividendHistory" sheetId="1" r:id="GemRid180757"/>
+    <sheet name="DividendHistory" sheetId="1" r:id="GemRid121458"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>XD Date</t>
   </si>
@@ -26,10 +26,13 @@
     <t>Gross Dividend</t>
   </si>
   <si>
+    <t>05/11/2025</t>
+  </si>
+  <si>
+    <t>0.002</t>
+  </si>
+  <si>
     <t>03/10/2025</t>
-  </si>
-  <si>
-    <t>0.002</t>
   </si>
   <si>
     <t>04/09/2025</t>
@@ -578,18 +581,18 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -600,7 +603,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -611,7 +614,7 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -622,7 +625,7 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -633,7 +636,7 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -644,7 +647,7 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -655,7 +658,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -666,7 +669,7 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -677,7 +680,7 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -688,7 +691,7 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -699,7 +702,7 @@
         <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -710,7 +713,7 @@
         <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -721,7 +724,7 @@
         <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
@@ -732,7 +735,7 @@
         <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -743,7 +746,7 @@
         <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -754,7 +757,7 @@
         <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -765,7 +768,7 @@
         <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -776,7 +779,7 @@
         <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -787,7 +790,7 @@
         <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -798,7 +801,7 @@
         <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
@@ -809,7 +812,7 @@
         <v>29</v>
       </c>
       <c r="C26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
@@ -820,7 +823,7 @@
         <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
@@ -831,18 +834,18 @@
         <v>31</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C29" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30">
@@ -853,7 +856,7 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
@@ -864,7 +867,7 @@
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
@@ -875,7 +878,7 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
@@ -886,7 +889,7 @@
         <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
@@ -897,7 +900,7 @@
         <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
@@ -908,7 +911,7 @@
         <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36">
@@ -919,7 +922,7 @@
         <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37">
@@ -930,7 +933,7 @@
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38">
@@ -941,7 +944,7 @@
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39">
@@ -952,7 +955,7 @@
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40">
@@ -963,18 +966,18 @@
         <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" t="s">
         <v>46</v>
-      </c>
-      <c r="B41" t="s">
-        <v>46</v>
-      </c>
-      <c r="C41" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="42">
@@ -985,7 +988,7 @@
         <v>47</v>
       </c>
       <c r="C42" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
@@ -996,7 +999,7 @@
         <v>48</v>
       </c>
       <c r="C43" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44">
@@ -1007,7 +1010,7 @@
         <v>49</v>
       </c>
       <c r="C44" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
@@ -1018,7 +1021,7 @@
         <v>50</v>
       </c>
       <c r="C45" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46">
@@ -1029,7 +1032,7 @@
         <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47">
@@ -1040,7 +1043,7 @@
         <v>52</v>
       </c>
       <c r="C47" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48">
@@ -1051,7 +1054,7 @@
         <v>53</v>
       </c>
       <c r="C48" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
@@ -1062,7 +1065,7 @@
         <v>54</v>
       </c>
       <c r="C49" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50">
@@ -1073,7 +1076,7 @@
         <v>55</v>
       </c>
       <c r="C50" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51">
@@ -1084,7 +1087,7 @@
         <v>56</v>
       </c>
       <c r="C51" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52">
@@ -1095,7 +1098,7 @@
         <v>57</v>
       </c>
       <c r="C52" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53">
@@ -1106,7 +1109,7 @@
         <v>58</v>
       </c>
       <c r="C53" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54">
@@ -1117,7 +1120,7 @@
         <v>59</v>
       </c>
       <c r="C54" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55">
@@ -1128,7 +1131,7 @@
         <v>60</v>
       </c>
       <c r="C55" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56">
@@ -1139,7 +1142,18 @@
         <v>61</v>
       </c>
       <c r="C56" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>62</v>
+      </c>
+      <c r="B57" t="s">
+        <v>62</v>
+      </c>
+      <c r="C57" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
